--- a/Team-Data/2007-08/1-22-2007-08.xlsx
+++ b/Team-Data/2007-08/1-22-2007-08.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -769,7 +836,7 @@
         <v>28</v>
       </c>
       <c r="AN2" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AO2" t="n">
         <v>2</v>
@@ -784,7 +851,7 @@
         <v>10</v>
       </c>
       <c r="AS2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AT2" t="n">
         <v>15</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>1-22-2007-08</t>
+          <t>2008-01-22</t>
         </is>
       </c>
     </row>
@@ -921,7 +988,7 @@
         <v>11.6</v>
       </c>
       <c r="AD3" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AE3" t="n">
         <v>1</v>
@@ -990,7 +1057,7 @@
         <v>19</v>
       </c>
       <c r="BA3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BB3" t="n">
         <v>12</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>1-22-2007-08</t>
+          <t>2008-01-22</t>
         </is>
       </c>
     </row>
@@ -1103,7 +1170,7 @@
         <v>-4</v>
       </c>
       <c r="AD4" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AE4" t="n">
         <v>21</v>
@@ -1148,13 +1215,13 @@
         <v>19</v>
       </c>
       <c r="AS4" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AT4" t="n">
         <v>28</v>
       </c>
       <c r="AU4" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AV4" t="n">
         <v>21</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>1-22-2007-08</t>
+          <t>2008-01-22</t>
         </is>
       </c>
     </row>
@@ -1285,7 +1352,7 @@
         <v>-3</v>
       </c>
       <c r="AD5" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AE5" t="n">
         <v>21</v>
@@ -1300,7 +1367,7 @@
         <v>5</v>
       </c>
       <c r="AI5" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AJ5" t="n">
         <v>6</v>
@@ -1309,7 +1376,7 @@
         <v>30</v>
       </c>
       <c r="AL5" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AM5" t="n">
         <v>23</v>
@@ -1330,7 +1397,7 @@
         <v>1</v>
       </c>
       <c r="AS5" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AT5" t="n">
         <v>7</v>
@@ -1357,7 +1424,7 @@
         <v>16</v>
       </c>
       <c r="BB5" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BC5" t="n">
         <v>21</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>1-22-2007-08</t>
+          <t>2008-01-22</t>
         </is>
       </c>
     </row>
@@ -1467,7 +1534,7 @@
         <v>-1.9</v>
       </c>
       <c r="AD6" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AE6" t="n">
         <v>13</v>
@@ -1482,13 +1549,13 @@
         <v>1</v>
       </c>
       <c r="AI6" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AJ6" t="n">
         <v>10</v>
       </c>
       <c r="AK6" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AL6" t="n">
         <v>14</v>
@@ -1506,7 +1573,7 @@
         <v>16</v>
       </c>
       <c r="AQ6" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AR6" t="n">
         <v>2</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>1-22-2007-08</t>
+          <t>2008-01-22</t>
         </is>
       </c>
     </row>
@@ -1649,7 +1716,7 @@
         <v>4.7</v>
       </c>
       <c r="AD7" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AE7" t="n">
         <v>5</v>
@@ -1673,13 +1740,13 @@
         <v>5</v>
       </c>
       <c r="AL7" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AM7" t="n">
         <v>19</v>
       </c>
       <c r="AN7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AO7" t="n">
         <v>6</v>
@@ -1715,7 +1782,7 @@
         <v>5</v>
       </c>
       <c r="AZ7" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BA7" t="n">
         <v>14</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>1-22-2007-08</t>
+          <t>2008-01-22</t>
         </is>
       </c>
     </row>
@@ -1831,7 +1898,7 @@
         <v>2.5</v>
       </c>
       <c r="AD8" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AE8" t="n">
         <v>11</v>
@@ -1843,7 +1910,7 @@
         <v>10</v>
       </c>
       <c r="AH8" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AI8" t="n">
         <v>5</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>1-22-2007-08</t>
+          <t>2008-01-22</t>
         </is>
       </c>
     </row>
@@ -2016,7 +2083,7 @@
         <v>3</v>
       </c>
       <c r="AE9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AF9" t="n">
         <v>5</v>
@@ -2025,7 +2092,7 @@
         <v>5</v>
       </c>
       <c r="AH9" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AI9" t="n">
         <v>15</v>
@@ -2034,7 +2101,7 @@
         <v>19</v>
       </c>
       <c r="AK9" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AL9" t="n">
         <v>19</v>
@@ -2043,7 +2110,7 @@
         <v>22</v>
       </c>
       <c r="AN9" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AO9" t="n">
         <v>12</v>
@@ -2070,7 +2137,7 @@
         <v>1</v>
       </c>
       <c r="AW9" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AX9" t="n">
         <v>12</v>
@@ -2082,7 +2149,7 @@
         <v>10</v>
       </c>
       <c r="BA9" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BB9" t="n">
         <v>14</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>1-22-2007-08</t>
+          <t>2008-01-22</t>
         </is>
       </c>
     </row>
@@ -2234,13 +2301,13 @@
         <v>14</v>
       </c>
       <c r="AQ10" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AR10" t="n">
         <v>8</v>
       </c>
       <c r="AS10" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AT10" t="n">
         <v>11</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>1-22-2007-08</t>
+          <t>2008-01-22</t>
         </is>
       </c>
     </row>
@@ -2377,7 +2444,7 @@
         <v>2</v>
       </c>
       <c r="AD11" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AE11" t="n">
         <v>13</v>
@@ -2440,7 +2507,7 @@
         <v>4</v>
       </c>
       <c r="AY11" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AZ11" t="n">
         <v>6</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>1-22-2007-08</t>
+          <t>2008-01-22</t>
         </is>
       </c>
     </row>
@@ -2565,13 +2632,13 @@
         <v>17</v>
       </c>
       <c r="AF12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AG12" t="n">
         <v>18</v>
       </c>
       <c r="AH12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AI12" t="n">
         <v>6</v>
@@ -2589,7 +2656,7 @@
         <v>3</v>
       </c>
       <c r="AN12" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AO12" t="n">
         <v>15</v>
@@ -2613,7 +2680,7 @@
         <v>6</v>
       </c>
       <c r="AV12" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AW12" t="n">
         <v>9</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>1-22-2007-08</t>
+          <t>2008-01-22</t>
         </is>
       </c>
     </row>
@@ -2774,7 +2841,7 @@
         <v>27</v>
       </c>
       <c r="AO13" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AP13" t="n">
         <v>9</v>
@@ -2789,7 +2856,7 @@
         <v>7</v>
       </c>
       <c r="AT13" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AU13" t="n">
         <v>17</v>
@@ -2813,7 +2880,7 @@
         <v>13</v>
       </c>
       <c r="BB13" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BC13" t="n">
         <v>24</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>1-22-2007-08</t>
+          <t>2008-01-22</t>
         </is>
       </c>
     </row>
@@ -2923,7 +2990,7 @@
         <v>6.3</v>
       </c>
       <c r="AD14" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AE14" t="n">
         <v>5</v>
@@ -2953,7 +3020,7 @@
         <v>8</v>
       </c>
       <c r="AN14" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AO14" t="n">
         <v>3</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>1-22-2007-08</t>
+          <t>2008-01-22</t>
         </is>
       </c>
     </row>
@@ -3105,7 +3172,7 @@
         <v>-3.6</v>
       </c>
       <c r="AD15" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AE15" t="n">
         <v>26</v>
@@ -3147,13 +3214,13 @@
         <v>17</v>
       </c>
       <c r="AR15" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AS15" t="n">
         <v>8</v>
       </c>
       <c r="AT15" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AU15" t="n">
         <v>19</v>
@@ -3171,7 +3238,7 @@
         <v>14</v>
       </c>
       <c r="AZ15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BA15" t="n">
         <v>12</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>1-22-2007-08</t>
+          <t>2008-01-22</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3354,7 @@
         <v>-6.6</v>
       </c>
       <c r="AD16" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AE16" t="n">
         <v>29</v>
@@ -3317,7 +3384,7 @@
         <v>25</v>
       </c>
       <c r="AN16" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AO16" t="n">
         <v>16</v>
@@ -3344,10 +3411,10 @@
         <v>14</v>
       </c>
       <c r="AW16" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AX16" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AY16" t="n">
         <v>2</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>1-22-2007-08</t>
+          <t>2008-01-22</t>
         </is>
       </c>
     </row>
@@ -3391,16 +3458,16 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E17" t="n">
         <v>16</v>
       </c>
       <c r="F17" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G17" t="n">
-        <v>0.381</v>
+        <v>0.39</v>
       </c>
       <c r="H17" t="n">
         <v>48.4</v>
@@ -3409,40 +3476,40 @@
         <v>36.3</v>
       </c>
       <c r="J17" t="n">
-        <v>80.5</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="K17" t="n">
-        <v>0.452</v>
+        <v>0.451</v>
       </c>
       <c r="L17" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="M17" t="n">
         <v>16</v>
       </c>
       <c r="N17" t="n">
-        <v>0.34</v>
+        <v>0.342</v>
       </c>
       <c r="O17" t="n">
-        <v>17</v>
+        <v>16.9</v>
       </c>
       <c r="P17" t="n">
-        <v>22.8</v>
+        <v>22.7</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.746</v>
+        <v>0.742</v>
       </c>
       <c r="R17" t="n">
-        <v>11.9</v>
+        <v>11.8</v>
       </c>
       <c r="S17" t="n">
         <v>28.6</v>
       </c>
       <c r="T17" t="n">
-        <v>40.5</v>
+        <v>40.4</v>
       </c>
       <c r="U17" t="n">
-        <v>21.4</v>
+        <v>21.3</v>
       </c>
       <c r="V17" t="n">
         <v>15.4</v>
@@ -3451,7 +3518,7 @@
         <v>6.8</v>
       </c>
       <c r="X17" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="Y17" t="n">
         <v>5.5</v>
@@ -3463,25 +3530,25 @@
         <v>20.4</v>
       </c>
       <c r="AB17" t="n">
-        <v>95.09999999999999</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="AC17" t="n">
         <v>-6</v>
       </c>
       <c r="AD17" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="AE17" t="n">
         <v>21</v>
       </c>
       <c r="AF17" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AG17" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AH17" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="AI17" t="n">
         <v>16</v>
@@ -3499,19 +3566,19 @@
         <v>24</v>
       </c>
       <c r="AN17" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AO17" t="n">
         <v>26</v>
       </c>
       <c r="AP17" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AQ17" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AR17" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AS17" t="n">
         <v>30</v>
@@ -3520,7 +3587,7 @@
         <v>27</v>
       </c>
       <c r="AU17" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AV17" t="n">
         <v>18</v>
@@ -3535,16 +3602,16 @@
         <v>25</v>
       </c>
       <c r="AZ17" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BA17" t="n">
         <v>20</v>
       </c>
       <c r="BB17" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BC17" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BD17" t="n">
         <v>10</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>1-22-2007-08</t>
+          <t>2008-01-22</t>
         </is>
       </c>
     </row>
@@ -3651,7 +3718,7 @@
         <v>-9.4</v>
       </c>
       <c r="AD18" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AE18" t="n">
         <v>30</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>1-22-2007-08</t>
+          <t>2008-01-22</t>
         </is>
       </c>
     </row>
@@ -3755,16 +3822,16 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E19" t="n">
         <v>18</v>
       </c>
       <c r="F19" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G19" t="n">
-        <v>0.439</v>
+        <v>0.45</v>
       </c>
       <c r="H19" t="n">
         <v>48.5</v>
@@ -3776,7 +3843,7 @@
         <v>77.3</v>
       </c>
       <c r="K19" t="n">
-        <v>0.435</v>
+        <v>0.434</v>
       </c>
       <c r="L19" t="n">
         <v>5.5</v>
@@ -3785,31 +3852,31 @@
         <v>17</v>
       </c>
       <c r="N19" t="n">
-        <v>0.326</v>
+        <v>0.323</v>
       </c>
       <c r="O19" t="n">
-        <v>20.6</v>
+        <v>20.8</v>
       </c>
       <c r="P19" t="n">
-        <v>28.7</v>
+        <v>28.9</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.717</v>
+        <v>0.72</v>
       </c>
       <c r="R19" t="n">
-        <v>11.6</v>
+        <v>11.7</v>
       </c>
       <c r="S19" t="n">
-        <v>29.8</v>
+        <v>30.1</v>
       </c>
       <c r="T19" t="n">
-        <v>41.4</v>
+        <v>41.8</v>
       </c>
       <c r="U19" t="n">
         <v>23.4</v>
       </c>
       <c r="V19" t="n">
-        <v>15.7</v>
+        <v>15.8</v>
       </c>
       <c r="W19" t="n">
         <v>6.7</v>
@@ -3824,28 +3891,28 @@
         <v>23</v>
       </c>
       <c r="AA19" t="n">
-        <v>23.2</v>
+        <v>23.4</v>
       </c>
       <c r="AB19" t="n">
         <v>93.40000000000001</v>
       </c>
       <c r="AC19" t="n">
-        <v>-6.2</v>
+        <v>-5.5</v>
       </c>
       <c r="AD19" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="AE19" t="n">
         <v>18</v>
       </c>
       <c r="AF19" t="n">
+        <v>18</v>
+      </c>
+      <c r="AG19" t="n">
         <v>19</v>
       </c>
-      <c r="AG19" t="n">
-        <v>20</v>
-      </c>
       <c r="AH19" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AI19" t="n">
         <v>30</v>
@@ -3854,34 +3921,34 @@
         <v>28</v>
       </c>
       <c r="AK19" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AL19" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AM19" t="n">
         <v>18</v>
       </c>
       <c r="AN19" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AO19" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AP19" t="n">
         <v>5</v>
       </c>
       <c r="AQ19" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AR19" t="n">
         <v>15</v>
       </c>
       <c r="AS19" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AT19" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="AU19" t="n">
         <v>5</v>
@@ -3893,10 +3960,10 @@
         <v>22</v>
       </c>
       <c r="AX19" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AY19" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AZ19" t="n">
         <v>26</v>
@@ -3905,10 +3972,10 @@
         <v>4</v>
       </c>
       <c r="BB19" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="BC19" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BD19" t="n">
         <v>10</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>1-22-2007-08</t>
+          <t>2008-01-22</t>
         </is>
       </c>
     </row>
@@ -4015,7 +4082,7 @@
         <v>5.5</v>
       </c>
       <c r="AD20" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AE20" t="n">
         <v>4</v>
@@ -4054,7 +4121,7 @@
         <v>30</v>
       </c>
       <c r="AQ20" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AR20" t="n">
         <v>16</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>1-22-2007-08</t>
+          <t>2008-01-22</t>
         </is>
       </c>
     </row>
@@ -4197,7 +4264,7 @@
         <v>-6.3</v>
       </c>
       <c r="AD21" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AE21" t="n">
         <v>25</v>
@@ -4245,7 +4312,7 @@
         <v>27</v>
       </c>
       <c r="AT21" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AU21" t="n">
         <v>30</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>1-22-2007-08</t>
+          <t>2008-01-22</t>
         </is>
       </c>
     </row>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>1-22-2007-08</t>
+          <t>2008-01-22</t>
         </is>
       </c>
     </row>
@@ -4567,16 +4634,16 @@
         <v>21</v>
       </c>
       <c r="AF23" t="n">
+        <v>25</v>
+      </c>
+      <c r="AG23" t="n">
         <v>24</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>23</v>
       </c>
       <c r="AH23" t="n">
         <v>22</v>
       </c>
       <c r="AI23" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AJ23" t="n">
         <v>16</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>1-22-2007-08</t>
+          <t>2008-01-22</t>
         </is>
       </c>
     </row>
@@ -4665,16 +4732,16 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E24" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F24" t="n">
         <v>12</v>
       </c>
       <c r="G24" t="n">
-        <v>0.714</v>
+        <v>0.707</v>
       </c>
       <c r="H24" t="n">
         <v>48.1</v>
@@ -4683,7 +4750,7 @@
         <v>41.8</v>
       </c>
       <c r="J24" t="n">
-        <v>85.2</v>
+        <v>85.3</v>
       </c>
       <c r="K24" t="n">
         <v>0.49</v>
@@ -4695,34 +4762,34 @@
         <v>23.4</v>
       </c>
       <c r="N24" t="n">
-        <v>0.387</v>
+        <v>0.385</v>
       </c>
       <c r="O24" t="n">
-        <v>17.5</v>
+        <v>17.3</v>
       </c>
       <c r="P24" t="n">
-        <v>22.4</v>
+        <v>22.3</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.781</v>
+        <v>0.777</v>
       </c>
       <c r="R24" t="n">
         <v>8.9</v>
       </c>
       <c r="S24" t="n">
-        <v>32.4</v>
+        <v>32.6</v>
       </c>
       <c r="T24" t="n">
-        <v>41.3</v>
+        <v>41.5</v>
       </c>
       <c r="U24" t="n">
-        <v>27.5</v>
+        <v>27.6</v>
       </c>
       <c r="V24" t="n">
         <v>13.3</v>
       </c>
       <c r="W24" t="n">
-        <v>7.3</v>
+        <v>7.2</v>
       </c>
       <c r="X24" t="n">
         <v>7</v>
@@ -4740,10 +4807,10 @@
         <v>110</v>
       </c>
       <c r="AC24" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="AD24" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="AE24" t="n">
         <v>2</v>
@@ -4773,16 +4840,16 @@
         <v>4</v>
       </c>
       <c r="AN24" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AO24" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AP24" t="n">
         <v>27</v>
       </c>
       <c r="AQ24" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AR24" t="n">
         <v>30</v>
@@ -4791,7 +4858,7 @@
         <v>6</v>
       </c>
       <c r="AT24" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AU24" t="n">
         <v>1</v>
@@ -4800,7 +4867,7 @@
         <v>6</v>
       </c>
       <c r="AW24" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AX24" t="n">
         <v>2</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>1-22-2007-08</t>
+          <t>2008-01-22</t>
         </is>
       </c>
     </row>
@@ -4925,7 +4992,7 @@
         <v>1.4</v>
       </c>
       <c r="AD25" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AE25" t="n">
         <v>9</v>
@@ -4946,7 +5013,7 @@
         <v>24</v>
       </c>
       <c r="AK25" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AL25" t="n">
         <v>11</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>1-22-2007-08</t>
+          <t>2008-01-22</t>
         </is>
       </c>
     </row>
@@ -5029,115 +5096,115 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E26" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F26" t="n">
         <v>22</v>
       </c>
       <c r="G26" t="n">
-        <v>0.45</v>
+        <v>0.436</v>
       </c>
       <c r="H26" t="n">
         <v>48.3</v>
       </c>
       <c r="I26" t="n">
-        <v>36</v>
+        <v>35.8</v>
       </c>
       <c r="J26" t="n">
-        <v>78.3</v>
+        <v>78.2</v>
       </c>
       <c r="K26" t="n">
-        <v>0.46</v>
+        <v>0.457</v>
       </c>
       <c r="L26" t="n">
-        <v>6.3</v>
+        <v>6.1</v>
       </c>
       <c r="M26" t="n">
-        <v>16.9</v>
+        <v>16.7</v>
       </c>
       <c r="N26" t="n">
-        <v>0.372</v>
+        <v>0.363</v>
       </c>
       <c r="O26" t="n">
         <v>21.6</v>
       </c>
       <c r="P26" t="n">
-        <v>26.9</v>
+        <v>27</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.8</v>
+        <v>0.799</v>
       </c>
       <c r="R26" t="n">
         <v>10</v>
       </c>
       <c r="S26" t="n">
-        <v>29.4</v>
+        <v>29.3</v>
       </c>
       <c r="T26" t="n">
-        <v>39.4</v>
+        <v>39.3</v>
       </c>
       <c r="U26" t="n">
-        <v>18.5</v>
+        <v>18.2</v>
       </c>
       <c r="V26" t="n">
-        <v>16.6</v>
+        <v>16.7</v>
       </c>
       <c r="W26" t="n">
-        <v>8.199999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="X26" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="Y26" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="Z26" t="n">
-        <v>22.5</v>
+        <v>22.6</v>
       </c>
       <c r="AA26" t="n">
-        <v>23</v>
+        <v>23.1</v>
       </c>
       <c r="AB26" t="n">
-        <v>99.90000000000001</v>
+        <v>99.2</v>
       </c>
       <c r="AC26" t="n">
-        <v>-1.9</v>
+        <v>-2.8</v>
       </c>
       <c r="AD26" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="AE26" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AF26" t="n">
         <v>18</v>
       </c>
       <c r="AG26" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AH26" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AI26" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="AJ26" t="n">
         <v>25</v>
       </c>
       <c r="AK26" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="AL26" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AM26" t="n">
         <v>20</v>
       </c>
       <c r="AN26" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="AO26" t="n">
         <v>5</v>
@@ -5146,13 +5213,13 @@
         <v>8</v>
       </c>
       <c r="AQ26" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AR26" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AS26" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AT26" t="n">
         <v>29</v>
@@ -5161,7 +5228,7 @@
         <v>29</v>
       </c>
       <c r="AV26" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AW26" t="n">
         <v>7</v>
@@ -5176,10 +5243,10 @@
         <v>24</v>
       </c>
       <c r="BA26" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BB26" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BC26" t="n">
         <v>19</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>1-22-2007-08</t>
+          <t>2008-01-22</t>
         </is>
       </c>
     </row>
@@ -5289,7 +5356,7 @@
         <v>5.6</v>
       </c>
       <c r="AD27" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AE27" t="n">
         <v>7</v>
@@ -5310,7 +5377,7 @@
         <v>23</v>
       </c>
       <c r="AK27" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AL27" t="n">
         <v>6</v>
@@ -5319,13 +5386,13 @@
         <v>6</v>
       </c>
       <c r="AN27" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AO27" t="n">
         <v>25</v>
       </c>
       <c r="AP27" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AQ27" t="n">
         <v>18</v>
@@ -5337,7 +5404,7 @@
         <v>12</v>
       </c>
       <c r="AT27" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AU27" t="n">
         <v>11</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>1-22-2007-08</t>
+          <t>2008-01-22</t>
         </is>
       </c>
     </row>
@@ -5471,7 +5538,7 @@
         <v>-8.5</v>
       </c>
       <c r="AD28" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AE28" t="n">
         <v>28</v>
@@ -5504,16 +5571,16 @@
         <v>21</v>
       </c>
       <c r="AO28" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AP28" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AQ28" t="n">
         <v>10</v>
       </c>
       <c r="AR28" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AS28" t="n">
         <v>2</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>1-22-2007-08</t>
+          <t>2008-01-22</t>
         </is>
       </c>
     </row>
@@ -5653,7 +5720,7 @@
         <v>2.1</v>
       </c>
       <c r="AD29" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AE29" t="n">
         <v>13</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>1-22-2007-08</t>
+          <t>2008-01-22</t>
         </is>
       </c>
     </row>
@@ -5877,7 +5944,7 @@
         <v>19</v>
       </c>
       <c r="AR30" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AS30" t="n">
         <v>28</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>1-22-2007-08</t>
+          <t>2008-01-22</t>
         </is>
       </c>
     </row>
@@ -6017,7 +6084,7 @@
         <v>2.9</v>
       </c>
       <c r="AD31" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AE31" t="n">
         <v>13</v>
@@ -6056,7 +6123,7 @@
         <v>19</v>
       </c>
       <c r="AQ31" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AR31" t="n">
         <v>9</v>
@@ -6080,7 +6147,7 @@
         <v>13</v>
       </c>
       <c r="AY31" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AZ31" t="n">
         <v>5</v>
@@ -6089,7 +6156,7 @@
         <v>26</v>
       </c>
       <c r="BB31" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BC31" t="n">
         <v>10</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>1-22-2007-08</t>
+          <t>2008-01-22</t>
         </is>
       </c>
     </row>
